--- a/tenders/Аукцион 223-ФЗ — сайт 17055043/02-estimate/СМЕТА-клиентская.xlsx
+++ b/tenders/Аукцион 223-ФЗ — сайт 17055043/02-estimate/СМЕТА-клиентская.xlsx
@@ -460,12 +460,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -486,14 +486,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Исполнитель: AIR / ООО «КСИИ» (НДС не облагается — резидент Сколково)</t>
+          <t>Исполнитель: SNAgency / ООО «Агентство «Социальные Сети»» (НДС 22%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Дата: 2026-08-10</t>
+          <t>Дата: 2026-08-11</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>210000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1070000</v>
+        <v>1210000</v>
       </c>
     </row>
     <row r="9" ht="45" customHeight="1">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1660000</v>
+        <v>1880000</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
@@ -592,11 +592,11 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Вёрстка, frontend, backend на 1С-Битрикс, интеграции, тестирование</t>
+          <t>Вёрстка, frontend, backend на 1С-Битрикс, регистрация/модерация производителей и студий, приём заявок на конкурс, интеграции, тестирование</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>2340000</v>
+        <v>2650000</v>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2730000</v>
+        <v>3090000</v>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
@@ -636,44 +636,91 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1170000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="8" t="n">
-        <v>9180000</v>
+        <v>1330000</v>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Лицензия ПО «1С-Битрикс: Управление сайтом», тариф «Бизнес»</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Лицензия предоставляется и оплачивается Исполнителем (уточнено заказчиком, ответ на запрос № 424331). Цена ориентировочная — сверить перед подачей</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Хостинг на период разработки и поддержки</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Сайт разворачивается на серверных мощностях Исполнителя (ответ на запрос № 424376). Оценка на ~12 месяцев — сверить перед подачей</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>60000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Налоговый режим: НДС не облагается (ст. 145.1 НК РФ, резидент Сколково)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Оплата — по факту сдачи-приёмки каждого этапа, без аванса, 7 рабочих дней с подписания акта</t>
-        </is>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО (с НДС 22%)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="8" t="n">
+        <v>10540000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Налоговый режим: НДС 22% (ООО «Агентство «Социальные Сети»»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Оплата — по факту сдачи-приёмки каждого этапа, без аванса, 7 рабочих дней с подписания акта</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Приёмка — 5 рабочих дней на этап, не более 2 итераций доработки (уточнено заказчиком)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Срок выполнения этапов 1–5: 220 рабочих дней с подписания контракта. Этап 6: 130 РД с ввода в эксплуатацию</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Смета предварительная, стартовая цена для аукциона — цена сложится по итогам торгов</t>
         </is>
